--- a/data/extracted/inventory-receipts/CONTENEDOR INTERLOCK 243 13 DE MARZO.XLSX
+++ b/data/extracted/inventory-receipts/CONTENEDOR INTERLOCK 243 13 DE MARZO.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556B864C-D20E-4388-9BB2-6FB5ABB368BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -725,7 +738,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -766,11 +779,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1051,50 +1063,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L194"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1132,12 +1144,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1175,7 +1187,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1213,7 +1225,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1251,7 +1263,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1289,7 +1301,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1327,7 +1339,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1365,7 +1377,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1403,7 +1415,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1441,7 +1453,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -1479,7 +1491,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1517,7 +1529,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -1555,7 +1567,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1593,7 +1605,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F19" s="1" t="s">
         <v>49</v>
       </c>
@@ -1613,7 +1625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F20" s="1" t="s">
         <v>51</v>
       </c>
@@ -1633,7 +1645,7 @@
         <v>226.7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1671,7 +1683,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -1709,7 +1721,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -1747,7 +1759,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,7 +1797,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1823,7 +1835,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -1861,7 +1873,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -1899,7 +1911,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -1937,7 +1949,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -1975,7 +1987,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -2013,7 +2025,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -2051,7 +2063,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -2089,7 +2101,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F33" s="1" t="s">
         <v>49</v>
       </c>
@@ -2109,7 +2121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F34" s="1" t="s">
         <v>51</v>
       </c>
@@ -2129,7 +2141,7 @@
         <v>224.2</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -2167,7 +2179,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -2205,7 +2217,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -2243,7 +2255,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -2281,7 +2293,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -2319,7 +2331,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -2357,7 +2369,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -2395,7 +2407,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -2433,7 +2445,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -2471,7 +2483,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -2509,7 +2521,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -2547,7 +2559,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -2585,7 +2597,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -2623,7 +2635,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -2661,7 +2673,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -2699,7 +2711,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -2737,7 +2749,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -2775,7 +2787,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -2813,7 +2825,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -2851,7 +2863,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -2889,7 +2901,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -2927,7 +2939,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -2965,7 +2977,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -3003,7 +3015,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -3041,7 +3053,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -3079,7 +3091,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F60" s="1" t="s">
         <v>49</v>
       </c>
@@ -3099,7 +3111,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F61" s="1" t="s">
         <v>108</v>
       </c>
@@ -3119,7 +3131,7 @@
         <v>463.5</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -3157,7 +3169,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -3195,7 +3207,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3233,7 +3245,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -3271,7 +3283,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -3309,7 +3321,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -3347,7 +3359,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -3385,7 +3397,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -3423,7 +3435,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -3461,7 +3473,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -3499,7 +3511,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -3537,7 +3549,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -3575,7 +3587,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -3613,7 +3625,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -3651,7 +3663,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -3689,7 +3701,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -3727,7 +3739,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -3765,7 +3777,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -3803,7 +3815,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -3841,7 +3853,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -3879,7 +3891,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -3917,7 +3929,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -3955,7 +3967,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -3993,7 +4005,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -4031,7 +4043,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -4069,7 +4081,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F87" s="1" t="s">
         <v>49</v>
       </c>
@@ -4089,7 +4101,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F88" s="1" t="s">
         <v>106</v>
       </c>
@@ -4112,7 +4124,7 @@
         <v>483.00000000000023</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -4150,7 +4162,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -4188,7 +4200,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -4226,7 +4238,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -4264,7 +4276,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -4302,7 +4314,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -4340,7 +4352,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -4378,7 +4390,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -4416,7 +4428,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -4454,7 +4466,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -4492,7 +4504,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -4530,7 +4542,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -4568,7 +4580,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -4606,7 +4618,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -4644,7 +4656,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -4682,7 +4694,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -4720,7 +4732,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -4758,7 +4770,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -4796,7 +4808,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -4834,7 +4846,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -4872,7 +4884,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -4910,7 +4922,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -4948,7 +4960,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -4986,7 +4998,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F112" s="1" t="s">
         <v>49</v>
       </c>
@@ -5006,7 +5018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F113" s="1" t="s">
         <v>163</v>
       </c>
@@ -5026,7 +5038,7 @@
         <v>414.3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -5064,7 +5076,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -5102,7 +5114,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -5140,7 +5152,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -5178,7 +5190,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -5216,7 +5228,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -5254,7 +5266,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -5292,7 +5304,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -5330,7 +5342,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -5368,7 +5380,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -5406,7 +5418,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -5444,7 +5456,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -5482,7 +5494,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -5520,7 +5532,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -5558,7 +5570,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -5596,7 +5608,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -5634,7 +5646,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -5672,7 +5684,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -5710,7 +5722,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -5748,7 +5760,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -5786,7 +5798,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -5824,7 +5836,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -5862,7 +5874,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -5900,7 +5912,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -5938,7 +5950,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -5976,7 +5988,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F139" s="1" t="s">
         <v>49</v>
       </c>
@@ -5996,7 +6008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F140" s="1" t="s">
         <v>106</v>
       </c>
@@ -6019,7 +6031,7 @@
         <v>486.50000000000023</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -6057,7 +6069,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -6095,7 +6107,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -6133,7 +6145,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -6171,7 +6183,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -6209,7 +6221,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -6247,7 +6259,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -6285,7 +6297,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -6323,7 +6335,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -6361,7 +6373,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -6399,7 +6411,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -6437,7 +6449,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -6475,7 +6487,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F153" s="1" t="s">
         <v>49</v>
       </c>
@@ -6495,7 +6507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F154" s="1" t="s">
         <v>51</v>
       </c>
@@ -6515,7 +6527,7 @@
         <v>221.7</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -6553,7 +6565,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -6591,7 +6603,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -6629,7 +6641,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -6667,7 +6679,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -6705,7 +6717,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -6743,7 +6755,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -6781,7 +6793,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -6819,7 +6831,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -6857,7 +6869,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -6895,7 +6907,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -6933,7 +6945,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -6971,7 +6983,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F167" s="1" t="s">
         <v>49</v>
       </c>
@@ -6991,7 +7003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F168" s="1" t="s">
         <v>51</v>
       </c>
@@ -7011,7 +7023,7 @@
         <v>224.2</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F169" s="1" t="s">
         <v>49</v>
       </c>
@@ -7031,12 +7043,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K170" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>221</v>
       </c>
@@ -7074,7 +7086,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F172" s="1" t="s">
         <v>49</v>
       </c>
@@ -7094,12 +7106,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K173" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>221</v>
       </c>
@@ -7137,7 +7149,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F175" s="1" t="s">
         <v>49</v>
       </c>
@@ -7157,7 +7169,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J176" s="2" t="s">
         <v>26</v>
       </c>
@@ -7165,7 +7177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>221</v>
       </c>
@@ -7203,7 +7215,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F178" s="1" t="s">
         <v>49</v>
       </c>
@@ -7223,7 +7235,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J179" s="2" t="s">
         <v>26</v>
       </c>
@@ -7231,7 +7243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>221</v>
       </c>
@@ -7269,7 +7281,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F181" s="1" t="s">
         <v>49</v>
       </c>
@@ -7289,12 +7301,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K182" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>221</v>
       </c>
@@ -7332,7 +7344,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F184" s="1" t="s">
         <v>49</v>
       </c>
@@ -7352,12 +7364,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K185" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>221</v>
       </c>
@@ -7395,7 +7407,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F187" s="1" t="s">
         <v>49</v>
       </c>
@@ -7415,12 +7427,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K188" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>221</v>
       </c>
@@ -7458,7 +7470,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F190" s="1" t="s">
         <v>49</v>
       </c>
@@ -7478,7 +7490,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J191" s="2" t="s">
         <v>26</v>
       </c>
@@ -7486,7 +7498,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>221</v>
       </c>
@@ -7524,7 +7536,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="193" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="6:12" x14ac:dyDescent="0.3">
       <c r="F193" s="1" t="s">
         <v>49</v>
       </c>
@@ -7544,7 +7556,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="6:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="6:12" x14ac:dyDescent="0.3">
       <c r="K194" s="2" t="s">
         <v>26</v>
       </c>
@@ -7553,4 +7565,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14ED6D5E-BEB7-45E0-861A-84AAF8E5D828}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47874</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>